--- a/results/review_queue.xlsx
+++ b/results/review_queue.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -913,6 +913,51 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>f8ea6afd-0701-4c49-83d8-31ed1f301699</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>the total fee for MCA semester 1 is 99000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>inline_table</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>[{"raw_text": "{\n  \"filters\": [{\"column\": \"program\", \"operator\": \"=\", \"value\": \"MCA\"}, {\"column\": \"semester\", \"operator\": \"=\", \"value\": 1}],\n  \"target_column\": \"total_fee\",\n  \"operation\": \"lookup\",\n  \"expected_value\": 99000,\n  \"comparator\": \"&lt;=\"\n}", "check": {"filters": [{"column": "program", "operator": "=", "value": "MCA"}, {"column": "semester", "operator": "=", "value": 1}], "target_column": "total_fee", "operation": "lookup", "expected_value": 99000, "comparator": "&lt;="}, "usage": {"input_tokens": 549, "output_tokens": 75}, "result": {"ok": true, "computed_value": 95000.0, "verdict": "TRUE", "error": null}}, {"raw_text": "{\n  \"filters\": [{\"column\": \"program\", \"operator\": \"contains\", \"value\": \"MCA\"}, {\"column\": \"semester\", \"operator\": \"==\", \"value\": 1}],\n  \"target_column\": \"total_fee\",\n  \"operation\": \"lookup\",\n  \"expected_value\": 99000,\n  \"comparator\": \"&lt;\"\n}", "check": {"filters": [{"column": "program", "operator": "contains", "value": "MCA"}, {"column": "semester", "operator": "==", "value": 1}], "target_column": "total_fee", "operation": "lookup", "expected_value": 99000, "comparator": "&lt;"}, "usage": {"input_tokens": 549, "output_tokens": 78}, "result": {"ok": true, "computed_value": 95000.0, "verdict": "TRUE", "error": null}}, {"raw_text": "{\n  \"filters\": [{\"column\": \"program\", \"operator\": \"=\", \"value\": \"MCA\"}, {\"column\": \"semester\", \"operator\": \"=\", \"value\": 1}],\n  \"target_column\": \"total_fee\",\n  \"operation\": \"lookup\",\n  \"expected_value\": 99000,\n  \"comparator\": \"&lt;\"\n}", "check": {"filters": [{"column": "program", "operator": "=", "value": "MCA"}, {"column": "semester", "operator": "=", "value": 1}], "target_column": "total_fee", "operation": "lookup", "expected_value": 99000, "comparator": "&lt;"}, "usage": {"input_tokens": 549, "output_tokens": 75}, "result": {"ok": true, "computed_value": 95000.0, "verdict": "TRUE", "error": null}}, {"raw_text": "{\n  \"filters\": [{\"column\": \"program\", \"operator\": \"=\", \"value\": \"MCA\"}, {\"column\": \"semester\", \"operator\": \"=\", \"value\": 1}],\n  \"target_column\": \"total_fee\",\n  \"operation\": \"lookup\",\n  \"expected_value\": 99000,\n  \"comparator\": \"&lt;=\"\n}", "check": {"filters": [{"column": "program", "operator": "=", "value": "MCA"}, {"column": "semester", "operator": "=", "value": 1}], "target_column": "total_fee", "operation": "lookup", "expected_value": 99000, "comparator": "&lt;="}, "usage": {"input_tokens": 549, "output_tokens": 75}, "result": {"ok": true, "computed_value": 95000.0, "verdict": "TRUE", "error": null}}, {"raw_text": "{\n  \"filters\": [{\"column\": \"program\", \"operator\": \"contains\", \"value\": \"MCA\"}, {\"column\": \"semester\", \"operator\": \"==\", \"value\": 1}],\n  \"target_column\": \"total_fee\",\n  \"operation\": \"compare\",\n  \"expected_value\": 99000,\n  \"comparator\": \"&lt;=\"\n}", "check": {"filters": [{"column": "program", "operator": "contains", "value": "MCA"}, {"column": "semester", "operator": "==", "value": 1}], "target_column": "total_fee", "operation": "compare", "expected_value": 99000, "comparator": "&lt;="}, "usage": {"input_tokens": 549, "output_tokens": 78}, "result": {"ok": false, "computed_value": null, "verdict": "INVALID", "error": "compare/difference needs &gt;=2 matching numeric rows"}}]</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>abstained: agreement below calibrated threshold (uncalibrated fallback threshold: requires full agreement)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:20:14.291213+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
